--- a/task.xlsx
+++ b/task.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{17129304-5679-4EDC-A4A6-B558810C8B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1890" windowWidth="29040" windowHeight="17520" xr2:uid="{A6B05049-76BD-4FE6-975A-B951ACF95D7B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A6B05049-76BD-4FE6-975A-B951ACF95D7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Task List" sheetId="2" r:id="rId1"/>
